--- a/attached_assets/pms_lead_grace_test_cases_1775120888910.xlsx
+++ b/attached_assets/pms_lead_grace_test_cases_1775120888910.xlsx
@@ -668,7 +668,7 @@
         <v>136 V4 calendar WOs correctly show Overdue. All have due dates in Jan/Feb 2026 (&gt;60 days ago). With Company Standard SPECIFIC_DATE_NEXT_MONTH=7, grace expired Mar 7 2026. All correctly Overdue after Apr 2 2026.</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>No defect observed.</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
@@ -974,7 +974,7 @@
         <v>Verified via code analysis: computeWorkOrderStatus() branches on maintenanceBasis at top level. Calendar settings changes cannot affect RH-based WOs. V4 RH WOs (7 Active, 6 Due) remain unchanged when calendar grace settings are modified.</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>No defect observed.</v>
       </c>
     </row>
     <row r="14" xml:space="preserve">
@@ -1104,7 +1104,7 @@
         <v>V11 has 4 RH WOs in Due status: MKR-IN-00073-702.005.02 (remaining=85h), MKR-IN-00073-702.005.01 (remaining=249h), MKR-IN-00026-601.001 (remaining=250h), MKR-RE-00039-601.002 (remaining=250h). All correctly computed with Company Standard lead=720h: 0≤remaining≤720 → Due.</v>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>No defect observed.</v>
       </c>
     </row>
     <row r="17" xml:space="preserve">
@@ -1146,7 +1146,7 @@
         <v>V11 has 3 RH WOs in Due (Grace P): JOB-TEST-MC-RH-50 WOs with dueRH=1000, currentRH=1055, remaining=-55. With Company Standard FIXED_HOURS 168h grace: -168≤-55&lt;0 → Due (Grace P). Correctly appear in Due tab with Grace P marker.</v>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>No defect observed.</v>
       </c>
     </row>
     <row r="18" xml:space="preserve">
@@ -1281,7 +1281,7 @@
         <v>Set Company Standard RH grace to FIXED_HOURS 100h. V11 JOB-TEST-MC-RH-50 WOs (remaining=-55): correctly show Due (Grace P) since -100≤-55&lt;0. Grace window correctly narrowed from 168h to 100h.</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>No defect observed.</v>
       </c>
     </row>
     <row r="21" xml:space="preserve">
@@ -1324,7 +1324,7 @@
         <v>Company Standard RH scope=ALL_WORK_ORDERS verified. All V11 RH WOs use same grace rule (100h). Due WOs (remaining≥0): correctly Due. Grace P WOs (remaining=-55): correctly Due (Grace P). No scope differentiation applied.</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>No defect observed.</v>
       </c>
     </row>
     <row r="22" xml:space="preserve">
@@ -1412,7 +1412,7 @@
         <v>Verified via code analysis: computeWorkOrderStatus() branches on maintenanceBasis. Calendar and RH paths are completely independent. Changing RH grace cannot affect calendar WO statuses.</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>No defect observed.</v>
       </c>
     </row>
     <row r="24" xml:space="preserve">
@@ -1459,7 +1459,7 @@
         <v>Set V4 to CUSTOM mode, calendarGraceMethod=FIXED_DAYS, calendarGraceValue=10. Settings saved successfully. All 136 V4 calendar WOs remain Overdue (correct—due Jan/Feb 2026, &gt;60 days past due, well beyond 10-day grace).</v>
       </c>
       <c r="M24" t="str">
-        <v/>
+        <v>No defect observed.</v>
       </c>
     </row>
     <row r="25" xml:space="preserve">
@@ -1501,7 +1501,7 @@
         <v>After V4 set to CUSTOM, V11 WOs unchanged: Due=6, Due (Grace P)=6, Overdue=1. V11 (no vessel settings) correctly continues using Company Standard. Custom changes isolated to V4.</v>
       </c>
       <c r="M25" t="str">
-        <v/>
+        <v>No defect observed.</v>
       </c>
     </row>
     <row r="26" xml:space="preserve">
@@ -1637,7 +1637,7 @@
         <v>Switched V4 from CUSTOM back to COMPANY_STANDARD. Settings saved: settingsMode=COMPANY_STANDARD. V4 WO statuses recalculated correctly. Mode switch correctly reverts to Company Standard grace rules.</v>
       </c>
       <c r="M28" t="str">
-        <v/>
+        <v>No defect observed.</v>
       </c>
     </row>
     <row r="29" xml:space="preserve">
@@ -1728,7 +1728,7 @@
         <v>Switched V4 from COMPANY_STANDARD to CUSTOM: calendarGraceMethod=FIXED_DAYS/14, rhGraceMethod=FIXED_HOURS/200h. Verified via GET: all custom values persisted correctly.</v>
       </c>
       <c r="M30" t="str">
-        <v/>
+        <v>No defect observed.</v>
       </c>
     </row>
     <row r="31" xml:space="preserve">
@@ -1774,7 +1774,7 @@
         <v>Company Standard round-trip: Saved SPECIFIC_DATE_NEXT_MONTH=7, rhGrace=168h. Re-read after save: identical values. All settings persist correctly across save/reopen.</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>No defect observed.</v>
       </c>
     </row>
     <row r="32" xml:space="preserve">
@@ -1820,7 +1820,7 @@
         <v>V4 custom settings persist after save: settingsMode=CUSTOM, calendarGraceValue=14, rhGraceValue=200. Round-trip save/reopen verified via GET.</v>
       </c>
       <c r="M32" t="str">
-        <v/>
+        <v>No defect observed.</v>
       </c>
     </row>
     <row r="33" xml:space="preserve">
@@ -1866,7 +1866,7 @@
         <v>V11 (no vessel settings) uses Company Standard by default. Company Standard persistence verified in TC-30. V11 inherits persisted values by fallback.</v>
       </c>
       <c r="M33" t="str">
-        <v/>
+        <v>No defect observed.</v>
       </c>
     </row>
     <row r="34" xml:space="preserve">
@@ -1909,7 +1909,7 @@
         <v>Vessel list API returns data for V4 and V11. V4: Active=10, Due=6, Overdue=136. V11: Due=6, Due (Grace P)=6, Overdue=1. Status summary reflects current work order states correctly.</v>
       </c>
       <c r="M34" t="str">
-        <v/>
+        <v>No defect observed.</v>
       </c>
     </row>
     <row r="35" xml:space="preserve">
@@ -1952,7 +1952,7 @@
         <v>API rejects FIXED_DAYS with graceValue=0 (HTTP 400: "Fixed Days requires a positive grace value"). Also rejects -5. Validation enforces graceValue≥1.</v>
       </c>
       <c r="M35" t="str">
-        <v/>
+        <v>No defect observed.</v>
       </c>
     </row>
     <row r="36" xml:space="preserve">
@@ -1995,7 +1995,7 @@
         <v>API rejects SPECIFIC_DATE_NEXT_MONTH with graceValue=0 and 29 (HTTP 400: "requires day value between 1 and 28"). Accepts graceValue=15 (HTTP 200). Range 1-28 enforced correctly.</v>
       </c>
       <c r="M36" t="str">
-        <v/>
+        <v>No defect observed.</v>
       </c>
     </row>
     <row r="37" xml:space="preserve">
@@ -2039,7 +2039,7 @@
         <v>Changed CS from SPECIFIC_DATE_NEXT_MONTH=7 to FIXED_DAYS=5. V11 Mar 17/24/25 WOs changed from Due (Grace P) to Overdue (5-day grace expired). After restoring SPECIFIC_DATE_NEXT_MONTH=7, WOs correctly reverted to Due (Grace P) (grace until Apr 7). forceRecalculation() triggers correctly after save.</v>
       </c>
       <c r="M37" t="str">
-        <v/>
+        <v>No defect observed.</v>
       </c>
     </row>
   </sheetData>
